--- a/data/trans_dic/IP11A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11A_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -659,27 +659,27 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>19,14%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 52,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,37</t>
+          <t>0,0; 25,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>3,31%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,15%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>1,73%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,24</t>
+          <t>0,0; 39,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,0</t>
+          <t>0,0; 63,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 9,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,87</t>
+          <t>0,0; 20,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 52,86</t>
+          <t>4,98; 42,91</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3,2%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 60,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,0</t>
+          <t>0,0; 16,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,45</t>
+          <t>0,0; 11,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,89</t>
+          <t>0,0; 26,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,76</t>
+          <t>0,0; 34,23</t>
         </is>
       </c>
     </row>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>26,13%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 35,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,3</t>
+          <t>0,0; 30,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,24</t>
+          <t>0,0; 76,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,6</t>
+          <t>0,0; 20,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,07</t>
+          <t>0,0; 20,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,3</t>
+          <t>0,0; 31,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,04; 10,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,85; 9,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,87</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>0,0; 24,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,72</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>3,33; 26,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,22</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,23</t>
+          <t>0,6; 5,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,65</t>
+          <t>0,57; 6,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,58</t>
+          <t>2,23; 13,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 17,59</t>
+          <t>2,51; 16,81</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1519,27 +1519,27 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1587,27 +1587,27 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>1339</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3595</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3659</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4137</t>
+          <t>0; 4355</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1790,37 +1790,37 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1849</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3494</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3637</t>
+          <t>0; 2279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3813</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2649</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3658</t>
+          <t>0; 2949</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3549</t>
+          <t>0; 3752</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3180</t>
+          <t>0; 4039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>584; 5514</t>
+          <t>519; 4467</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,62 +1993,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>487</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>988</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2714</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3110</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3019</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4537</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2732</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3467</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2922</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4453</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2588</t>
+          <t>0; 2478</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2783</t>
+          <t>0; 3082</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2704</t>
+          <t>0; 3273</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5157</t>
+          <t>0; 4740</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2201,37 +2201,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4064</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2343</t>
+          <t>0; 3572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2289,17 +2289,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3458</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6289</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3912</t>
+          <t>0; 2264</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6119</t>
+          <t>0; 6534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4461</t>
+          <t>0; 4587</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2341,37 +2341,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2409,49 +2409,49 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>3230</t>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>485; 4975</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4234</t>
+          <t>626; 7305</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>765; 6280</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 5363</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>481; 4861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>632; 7867</t>
+          <t>0; 3544</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>778; 6218</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5821</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>485; 5099</t>
+          <t>488; 4903</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>712; 8323</t>
+          <t>713; 8145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1426; 7423</t>
+          <t>1428; 8407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1024; 7244</t>
+          <t>990; 6628</t>
         </is>
       </c>
     </row>
